--- a/data.xlsx
+++ b/data.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="448">
   <si>
     <t/>
   </si>
@@ -114,7 +114,7 @@
     <t>铺场后使用群体贴膜，带来极高收益和优势，但是害怕丢线，抗快偏弱</t>
   </si>
   <si>
-    <t>杨华童学</t>
+    <t>美前不是区</t>
   </si>
   <si>
     <t>美苏茄子*</t>
@@ -312,7 +312,7 @@
     <t>天气控场，肘击快攻，飞燕剃头，吴迪</t>
   </si>
   <si>
-    <t>蒙帝</t>
+    <t>老前辈</t>
   </si>
   <si>
     <t>苏日控制</t>
@@ -378,13 +378,13 @@
     <t>德法断爆*</t>
   </si>
   <si>
-    <t>%%16|2h2i3d3m3n4zgUtgu0vgwCwLz6;2l2n2N3h3i3jfUgJoXtdvh;;oG</t>
+    <t>%%16|2i2P343O3Y4zgUnDq9tgu0wJwL;2l3i3jgJoPtd;3hgQ;oGoX</t>
   </si>
   <si>
     <t>娱乐 中速 慢速</t>
   </si>
   <si>
-    <t>敌人断水则继续断，敌人爆牌则继续爆，纯为报复社会的卡组，不为输赢</t>
+    <t>敌人断水则断，敌人爆牌则爆，纯为报复社会的卡组，不为输赢</t>
   </si>
   <si>
     <t>私禾之源</t>
@@ -402,7 +402,7 @@
     <t>苏美自残*</t>
   </si>
   <si>
-    <t>%%45|828C8gg6pDppqTz0;mFnU;o6;7H8I9ngbiQmo</t>
+    <t>%%45|8CfxiP;9no6vfz0;8IiQmonU;7H9mgbrg</t>
   </si>
   <si>
     <t>血与铁时期的毒瘤轮椅在预备依旧发光发热</t>
@@ -414,7 +414,7 @@
     <t>%%31|2S5C6B6y7ahHm6qDrktCvhx0zq;7qlkqCtGx3;4p6x7e7l;5Z</t>
   </si>
   <si>
-    <t>永不落幕的传卡组</t>
+    <t>永不落幕的传奇卡组</t>
   </si>
   <si>
     <t>英德一攻*</t>
@@ -444,7 +444,7 @@
     <t>美法前线</t>
   </si>
   <si>
-    <t>%%56|bBbEcrcTfLjylIrcrSvcvWxjyS;bIbqcVd6lgsG;dvvS;d4rV</t>
+    <t>%%56|bElFu8v6v7xA;bqd4d6qZrcvc;bIxcxj;dvrVvS</t>
   </si>
   <si>
     <t>中速 快攻</t>
@@ -480,7 +480,7 @@
     <t>日波炸槽</t>
   </si>
   <si>
-    <t>%%38|5Cp2;5B6wp4petFzw;5Zp1p6zizpzszt;pc</t>
+    <t>%%38|5B5Cm6p2p4rkwXzq;6w6xpetFzizsztzw;5Zp1p6pczp;</t>
   </si>
   <si>
     <t>炸槽无敌，现役轮椅之一</t>
@@ -671,10 +671,6 @@
     <t>实力还在，仍有一战之力</t>
   </si>
   <si>
-    <t>敌人断水则断，爆牌则爆牌，诸多卡牌
-社会的卡组</t>
-  </si>
-  <si>
     <t>英美跳枪*</t>
   </si>
   <si>
@@ -1110,9 +1106,6 @@
     <t>英日压制*</t>
   </si>
   <si>
-    <t>%%23|0m0w0z1lgvlrnQv8yJ;0s1a1V5W6N7ejOpQpWwbwW;;0omU</t>
-  </si>
-  <si>
     <t>点击输入文字 木昆木 请输入文本</t>
   </si>
   <si>
@@ -1266,6 +1259,15 @@
     <t>%%17|2Z3m3Q3Y4r5seYianwu0wJxr;3f4pi7jJmTnCoPvhwKxo;5k;2V</t>
   </si>
   <si>
+    <t>变速 娱乐</t>
+  </si>
+  <si>
+    <t>一万个兵种作战，但是比较笨</t>
+  </si>
+  <si>
+    <t>古德不帅</t>
+  </si>
+  <si>
     <t>英法控*</t>
   </si>
   <si>
@@ -1275,25 +1277,89 @@
     <t>金卡含量很高（很多可以优化），然后塞屎控制双轴的，因为回血量高所以带了邦作为终端，也可以去掉纯控制</t>
   </si>
   <si>
-    <t>%%16|2i2P343O3Y4zgUnDq9tgu0wJwL;2l3i3jgJoPtd;3hgQ;oGoX</t>
-  </si>
-  <si>
-    <t>敌人断水则断，敌人爆牌则爆，纯为报复社会的卡组，不为输赢</t>
-  </si>
-  <si>
-    <t>永不落幕的传奇卡组</t>
-  </si>
-  <si>
-    <t>美前不是区</t>
-  </si>
-  <si>
-    <t>%%45|8CfxiP;9no6vfz0;8IiQmonU;7H9mgbrg</t>
-  </si>
-  <si>
-    <t>%%56|bElFu8v6v7xA;bqd4d6qZrcvc;bIxcxj;dvrVvS</t>
-  </si>
-  <si>
-    <t>%%38|5B5Cm6p2p4rkwXzq;6w6xpetFzizsztzw;5Zp1p6pczp;</t>
+    <t>美法炮</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+%%56|bEbmbpbqcpd6gQj4ohsGvcvU;2id4d7lgr4;vSxcxj;glrc</t>
+  </si>
+  <si>
+    <t>造价便宜 退环境 通过炮兵马奇诺贴膜输出及斩杀</t>
+  </si>
+  <si>
+    <t>周平王</t>
+  </si>
+  <si>
+    <t>美法布列塔尼（惩戒）</t>
+  </si>
+  <si>
+    <t>%%56|2nbCbEcPDCfGh9jvmKpyr3rQsytYv6yv;2i2l2xggofpDpJ;bKbPj1;</t>
+  </si>
+  <si>
+    <t>跳费  布列塔尼  高费指令打伤害</t>
+  </si>
+  <si>
+    <t>TO</t>
+  </si>
+  <si>
+    <t>日波军团*预备版</t>
+  </si>
+  <si>
+    <t>%%38|5C5V6BE7iHjjlfmanPqDrkwXx3znzq;iDjOnOphtGtyzs;E9tK;pg</t>
+  </si>
+  <si>
+    <t>中速铺场</t>
+  </si>
+  <si>
+    <t>铺场造大哥，闪电征服斩杀，但被撤退克制</t>
+  </si>
+  <si>
+    <t>日美跳茄</t>
+  </si>
+  <si>
+    <t>%%35|5C5F5M5x5z63666B7b7xggjjlfmcnPr6rkx9znzv;bqj1jOmax3;bKtKu3;</t>
+  </si>
+  <si>
+    <t>跳费</t>
+  </si>
+  <si>
+    <t>前期跳费，后期配合茄子天气以及大飞机岚兵斩杀，娱乐性强的同时有一定强度，克制英国</t>
+  </si>
+  <si>
+    <t>特化美英惩戒</t>
+  </si>
+  <si>
+    <t>%%52|bCbTbmcPdkh9jvpyv6vX;mUst;bPczeHmIpJvUw2;DR</t>
+  </si>
+  <si>
+    <t>经过西非特化构筑后的惩戒，强度不算高，但是很神圣</t>
+  </si>
+  <si>
+    <t>德美暂避工厂*</t>
+  </si>
+  <si>
+    <t>%%15|2Z4zbPcqgUttu0wCz6zb;2Yj1mDvhyzzd;q8uxwB;bKwM</t>
+  </si>
+  <si>
+    <t>在暂避锋芒改版之后，我们可以复制蓝色军团，446等单位，</t>
+  </si>
+  <si>
+    <t>苏波转换</t>
+  </si>
+  <si>
+    <t>%%48|8CfrjWppqTrjt3tatmu4vewqwyyXz5zi;8Ns0t5tyww;88E5zC;u5</t>
+  </si>
+  <si>
+    <t>用424转红溃军，0011。单位交换应该行</t>
+  </si>
+  <si>
+    <t>在暂避锋芒改版之后，我们可以复制蓝色军团，446等单位，还有第二战线，可以做到拉一堆蓝色军团进行走路，还有美国的445可以帮我们减伤</t>
+  </si>
+  <si>
+    <t>在暂避锋芒改版之后，我们可以复制蓝色军团，446等单位，还有第二战线，可以做到拉一堆蓝色军团进行走路，还有美国的445可以帮我们减伤，然后可以靠山东孔夫子斩杀，当然也可以造一堆雷霆大德伞（笑）</t>
+  </si>
+  <si>
+    <t>中速 铺场</t>
   </si>
 </sst>
 </file>
@@ -1363,9 +1429,6 @@
       <sz val="18"/>
     </font>
     <font>
-      <sz val="16"/>
-    </font>
-    <font>
       <color rgb="FF000000"/>
       <sz val="20"/>
     </font>
@@ -1375,6 +1438,9 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <sz val="16"/>
+    </font>
+    <font>
       <sz val="16"/>
     </font>
     <font>
@@ -1452,7 +1518,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1531,19 +1597,34 @@
     <xf fontId="15" fillId="4" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="16" fillId="4" borderId="0" xfId="0">
+    <xf fontId="16" fillId="2" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="17" fillId="2" borderId="0" xfId="0">
+    <xf fontId="17" fillId="4" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="18" fillId="4" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="0"/>
+    </xf>
     <xf fontId="8" fillId="3" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="4" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="4" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="10" fillId="6" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="2" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="8" fillId="5" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="19" fillId="4" borderId="0" xfId="0">
@@ -1810,11 +1891,11 @@
   <dimension ref="E299"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="18.2109" style="32" customWidth="1"/>
-    <col min="2" max="2" width="36.4219" style="33" customWidth="1"/>
-    <col min="3" max="3" width="38.0312" style="34" customWidth="1"/>
-    <col min="4" max="4" width="53.0469" style="35" customWidth="1"/>
-    <col min="5" max="5" width="34.2617" style="35" customWidth="1"/>
+    <col min="1" max="1" width="18.2109" style="37" customWidth="1"/>
+    <col min="2" max="2" width="36.4219" style="38" customWidth="1"/>
+    <col min="3" max="3" width="38.0312" style="39" customWidth="1"/>
+    <col min="4" max="4" width="53.0469" style="40" customWidth="1"/>
+    <col min="5" max="5" width="34.2617" style="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="60" customHeight="1">
@@ -1933,7 +2014,7 @@
         <v>32</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>422</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="60" customHeight="1">
@@ -2315,13 +2396,13 @@
         <v>120</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>419</v>
+        <v>121</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>122</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>420</v>
+        <v>123</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>124</v>
@@ -2349,7 +2430,7 @@
         <v>128</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>423</v>
+        <v>129</v>
       </c>
       <c r="C32" s="10" t="s">
         <v>56</v>
@@ -2372,7 +2453,7 @@
         <v>22</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>421</v>
+        <v>133</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>19</v>
@@ -2417,7 +2498,7 @@
         <v>142</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>424</v>
+        <v>143</v>
       </c>
       <c r="C36" s="17" t="s">
         <v>144</v>
@@ -2468,7 +2549,7 @@
         <v>154</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>425</v>
+        <v>155</v>
       </c>
       <c r="C39" s="15" t="s">
         <v>22</v>
@@ -2620,7 +2701,7 @@
       <c r="A48" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="B48" s="13" t="s">
+      <c r="B48" s="19" t="s">
         <v>185</v>
       </c>
       <c r="C48" s="10" t="s">
@@ -2788,101 +2869,101 @@
     </row>
     <row r="58" spans="1:5" ht="60" customHeight="1">
       <c r="A58" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B58" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="B58" s="20" t="s">
+      <c r="C58" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="D58" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="D58" s="12" t="s">
+      <c r="E58" s="5" t="s">
         <v>222</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="60" customHeight="1">
       <c r="A59" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="B59" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="B59" s="19" t="s">
+      <c r="C59" s="24" t="s">
         <v>225</v>
       </c>
-      <c r="C59" s="25" t="s">
+      <c r="D59" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="E59" s="25" t="s">
         <v>227</v>
-      </c>
-      <c r="E59" s="26" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="60" customHeight="1">
       <c r="A60" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B60" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="B60" s="20" t="s">
+      <c r="C60" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="D60" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="D60" s="12" t="s">
-        <v>232</v>
-      </c>
       <c r="E60" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="60" customHeight="1">
       <c r="A61" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="B61" s="19" t="s">
         <v>233</v>
-      </c>
-      <c r="B61" s="13" t="s">
-        <v>234</v>
       </c>
       <c r="C61" s="17" t="s">
         <v>22</v>
       </c>
       <c r="D61" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="E61" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="E61" s="11" t="s">
+    </row>
+    <row r="62" spans="1:5" ht="60" customHeight="1">
+      <c r="A62" s="26" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" ht="60" customHeight="1">
-      <c r="A62" s="27" t="s">
+      <c r="B62" s="20" t="s">
         <v>237</v>
-      </c>
-      <c r="B62" s="20" t="s">
-        <v>238</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>173</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="60" customHeight="1">
       <c r="A63" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="B63" s="19" t="s">
         <v>240</v>
-      </c>
-      <c r="B63" s="19" t="s">
-        <v>241</v>
       </c>
       <c r="C63" s="10" t="s">
         <v>173</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E63" s="11" t="s">
         <v>171</v>
@@ -2890,16 +2971,16 @@
     </row>
     <row r="64" spans="1:5" ht="60" customHeight="1">
       <c r="A64" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B64" s="20" t="s">
         <v>243</v>
-      </c>
-      <c r="B64" s="20" t="s">
-        <v>244</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>173</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E64" s="5" t="s">
         <v>171</v>
@@ -2907,16 +2988,16 @@
     </row>
     <row r="65" spans="1:5" ht="60" customHeight="1">
       <c r="A65" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="B65" s="19" t="s">
         <v>246</v>
-      </c>
-      <c r="B65" s="19" t="s">
-        <v>247</v>
       </c>
       <c r="C65" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E65" s="11" t="s">
         <v>171</v>
@@ -2924,16 +3005,16 @@
     </row>
     <row r="66" spans="1:5" ht="60" customHeight="1">
       <c r="A66" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B66" s="20" t="s">
         <v>249</v>
-      </c>
-      <c r="B66" s="20" t="s">
-        <v>250</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>79</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>214</v>
@@ -2941,16 +3022,16 @@
     </row>
     <row r="67" spans="1:5" ht="60" customHeight="1">
       <c r="A67" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="B67" s="19" t="s">
         <v>252</v>
-      </c>
-      <c r="B67" s="13" t="s">
-        <v>253</v>
       </c>
       <c r="C67" s="10" t="s">
         <v>173</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E67" s="11" t="s">
         <v>10</v>
@@ -2958,16 +3039,16 @@
     </row>
     <row r="68" spans="1:5" ht="60" customHeight="1">
       <c r="A68" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B68" s="20" t="s">
         <v>255</v>
-      </c>
-      <c r="B68" s="14" t="s">
-        <v>256</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>173</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>171</v>
@@ -2975,16 +3056,16 @@
     </row>
     <row r="69" spans="1:5" ht="60" customHeight="1">
       <c r="A69" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="B69" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="B69" s="13" t="s">
+      <c r="C69" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="C69" s="10" t="s">
+      <c r="D69" s="11" t="s">
         <v>260</v>
-      </c>
-      <c r="D69" s="11" t="s">
-        <v>261</v>
       </c>
       <c r="E69" s="11" t="s">
         <v>214</v>
@@ -2992,16 +3073,16 @@
     </row>
     <row r="70" spans="1:5" ht="60" customHeight="1">
       <c r="A70" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B70" s="20" t="s">
         <v>262</v>
-      </c>
-      <c r="B70" s="14" t="s">
-        <v>263</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>52</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E70" s="5" t="s">
         <v>171</v>
@@ -3009,16 +3090,16 @@
     </row>
     <row r="71" spans="1:5" ht="60" customHeight="1">
       <c r="A71" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="B71" s="19" t="s">
         <v>265</v>
       </c>
-      <c r="B71" s="13" t="s">
+      <c r="C71" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="C71" s="10" t="s">
+      <c r="D71" s="27" t="s">
         <v>267</v>
-      </c>
-      <c r="D71" s="24" t="s">
-        <v>268</v>
       </c>
       <c r="E71" s="11" t="s">
         <v>10</v>
@@ -3026,16 +3107,16 @@
     </row>
     <row r="72" spans="1:5" ht="60" customHeight="1">
       <c r="A72" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B72" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="B72" s="14" t="s">
+      <c r="C72" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C72" s="5" t="s">
+      <c r="D72" s="5" t="s">
         <v>271</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>272</v>
       </c>
       <c r="E72" s="5" t="s">
         <v>214</v>
@@ -3043,16 +3124,16 @@
     </row>
     <row r="73" spans="1:5" ht="60" customHeight="1">
       <c r="A73" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="B73" s="19" t="s">
         <v>273</v>
-      </c>
-      <c r="B73" s="13" t="s">
-        <v>274</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>52</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E73" s="11" t="s">
         <v>10</v>
@@ -3060,33 +3141,33 @@
     </row>
     <row r="74" spans="1:5" ht="60" customHeight="1">
       <c r="A74" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B74" s="20" t="s">
         <v>276</v>
-      </c>
-      <c r="B74" s="14" t="s">
-        <v>277</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>52</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="60" customHeight="1">
       <c r="A75" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="B75" s="19" t="s">
         <v>279</v>
       </c>
-      <c r="B75" s="13" t="s">
+      <c r="C75" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="D75" s="11" t="s">
         <v>280</v>
-      </c>
-      <c r="C75" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="D75" s="11" t="s">
-        <v>281</v>
       </c>
       <c r="E75" s="11" t="s">
         <v>10</v>
@@ -3094,16 +3175,16 @@
     </row>
     <row r="76" spans="1:5" ht="60" customHeight="1">
       <c r="A76" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B76" s="20" t="s">
         <v>282</v>
-      </c>
-      <c r="B76" s="14" t="s">
-        <v>283</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>52</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E76" s="5" t="s">
         <v>214</v>
@@ -3111,16 +3192,16 @@
     </row>
     <row r="77" spans="1:5" ht="60" customHeight="1">
       <c r="A77" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="B77" s="19" t="s">
         <v>285</v>
-      </c>
-      <c r="B77" s="13" t="s">
-        <v>286</v>
       </c>
       <c r="C77" s="10" t="s">
         <v>173</v>
       </c>
       <c r="D77" s="28" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E77" s="11" t="s">
         <v>214</v>
@@ -3128,33 +3209,33 @@
     </row>
     <row r="78" spans="1:5" ht="60" customHeight="1">
       <c r="A78" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="B78" s="29" t="s">
         <v>288</v>
-      </c>
-      <c r="B78" s="14" t="s">
-        <v>289</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>52</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="60" customHeight="1">
       <c r="A79" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="B79" s="19" t="s">
         <v>291</v>
-      </c>
-      <c r="B79" s="13" t="s">
-        <v>292</v>
       </c>
       <c r="C79" s="10" t="s">
         <v>173</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E79" s="11" t="s">
         <v>171</v>
@@ -3162,33 +3243,33 @@
     </row>
     <row r="80" spans="1:5" ht="60" customHeight="1">
       <c r="A80" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B80" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="B80" s="14" t="s">
+      <c r="C80" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="C80" s="5" t="s">
+      <c r="D80" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="D80" s="5" t="s">
+      <c r="E80" s="5" t="s">
         <v>297</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="60" customHeight="1">
       <c r="A81" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="B81" s="13" t="s">
         <v>299</v>
-      </c>
-      <c r="B81" s="13" t="s">
-        <v>300</v>
       </c>
       <c r="C81" s="10" t="s">
         <v>173</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E81" s="11" t="s">
         <v>46</v>
@@ -3196,16 +3277,16 @@
     </row>
     <row r="82" spans="1:5" ht="60" customHeight="1">
       <c r="A82" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B82" s="14" t="s">
         <v>302</v>
       </c>
-      <c r="B82" s="14" t="s">
+      <c r="C82" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="D82" s="5" t="s">
         <v>303</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>304</v>
       </c>
       <c r="E82" s="5" t="s">
         <v>10</v>
@@ -3213,16 +3294,16 @@
     </row>
     <row r="83" spans="1:5" ht="60" customHeight="1">
       <c r="A83" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="B83" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="B83" s="29" t="s">
+      <c r="C83" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="C83" s="11" t="s">
+      <c r="D83" s="9" t="s">
         <v>307</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>308</v>
       </c>
       <c r="E83" s="11" t="s">
         <v>171</v>
@@ -3230,16 +3311,16 @@
     </row>
     <row r="84" spans="1:5" ht="60" customHeight="1">
       <c r="A84" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B84" s="14" t="s">
         <v>309</v>
-      </c>
-      <c r="B84" s="14" t="s">
-        <v>310</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>52</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>10</v>
@@ -3247,16 +3328,16 @@
     </row>
     <row r="85" spans="1:5" ht="60" customHeight="1">
       <c r="A85" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="B85" s="13" t="s">
         <v>312</v>
-      </c>
-      <c r="B85" s="13" t="s">
-        <v>313</v>
       </c>
       <c r="C85" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D85" s="30" t="s">
-        <v>314</v>
+      <c r="D85" s="31" t="s">
+        <v>313</v>
       </c>
       <c r="E85" s="11">
         <v>114514</v>
@@ -3264,16 +3345,16 @@
     </row>
     <row r="86" spans="1:5" ht="60" customHeight="1">
       <c r="A86" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B86" s="14" t="s">
         <v>315</v>
-      </c>
-      <c r="B86" s="14" t="s">
-        <v>316</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>173</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E86" s="5" t="s">
         <v>19</v>
@@ -3281,16 +3362,16 @@
     </row>
     <row r="87" spans="1:5" ht="60" customHeight="1">
       <c r="A87" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="B87" s="13" t="s">
         <v>318</v>
-      </c>
-      <c r="B87" s="13" t="s">
-        <v>319</v>
       </c>
       <c r="C87" s="17" t="s">
         <v>22</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E87" s="11" t="s">
         <v>214</v>
@@ -3298,16 +3379,16 @@
     </row>
     <row r="88" spans="1:5" ht="60" customHeight="1">
       <c r="A88" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B88" s="14" t="s">
         <v>321</v>
-      </c>
-      <c r="B88" s="14" t="s">
-        <v>322</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>173</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E88" s="5" t="s">
         <v>19</v>
@@ -3315,16 +3396,16 @@
     </row>
     <row r="89" spans="1:5" ht="60" customHeight="1">
       <c r="A89" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="B89" s="13" t="s">
         <v>324</v>
       </c>
-      <c r="B89" s="13" t="s">
+      <c r="C89" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="D89" s="11" t="s">
         <v>325</v>
-      </c>
-      <c r="C89" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="D89" s="11" t="s">
-        <v>326</v>
       </c>
       <c r="E89" s="11" t="s">
         <v>171</v>
@@ -3332,33 +3413,33 @@
     </row>
     <row r="90" spans="1:5" ht="60" customHeight="1">
       <c r="A90" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B90" s="14" t="s">
         <v>327</v>
-      </c>
-      <c r="B90" s="14" t="s">
-        <v>328</v>
       </c>
       <c r="C90" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D90" s="27" t="s">
-        <v>329</v>
+      <c r="D90" s="26" t="s">
+        <v>328</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="60" customHeight="1">
       <c r="A91" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="B91" s="13" t="s">
         <v>330</v>
-      </c>
-      <c r="B91" s="13" t="s">
-        <v>331</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>173</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>19</v>
@@ -3366,16 +3447,16 @@
     </row>
     <row r="92" spans="1:5" ht="60" customHeight="1">
       <c r="A92" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B92" s="14" t="s">
         <v>333</v>
       </c>
-      <c r="B92" s="14" t="s">
+      <c r="C92" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="C92" s="5" t="s">
+      <c r="D92" s="5" t="s">
         <v>335</v>
-      </c>
-      <c r="D92" s="5" t="s">
-        <v>336</v>
       </c>
       <c r="E92" s="5" t="s">
         <v>19</v>
@@ -3383,33 +3464,33 @@
     </row>
     <row r="93" spans="1:5" ht="60" customHeight="1">
       <c r="A93" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="B93" s="9" t="s">
         <v>337</v>
-      </c>
-      <c r="B93" s="9" t="s">
-        <v>338</v>
       </c>
       <c r="C93" s="10" t="s">
         <v>199</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E93" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="60" customHeight="1">
       <c r="A94" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="B94" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="B94" s="14" t="s">
+      <c r="C94" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="C94" s="5" t="s">
+      <c r="D94" s="5" t="s">
         <v>342</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>343</v>
       </c>
       <c r="E94" s="5" t="s">
         <v>19</v>
@@ -3417,16 +3498,16 @@
     </row>
     <row r="95" spans="1:5" ht="60" customHeight="1">
       <c r="A95" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="B95" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="B95" s="9" t="s">
+      <c r="C95" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="D95" s="11" t="s">
         <v>345</v>
-      </c>
-      <c r="C95" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="D95" s="11" t="s">
-        <v>346</v>
       </c>
       <c r="E95" s="11" t="s">
         <v>214</v>
@@ -3434,16 +3515,16 @@
     </row>
     <row r="96" spans="1:5" ht="60" customHeight="1">
       <c r="A96" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B96" s="12" t="s">
         <v>347</v>
-      </c>
-      <c r="B96" s="12" t="s">
-        <v>348</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>122</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E96" s="5" t="s">
         <v>171</v>
@@ -3451,16 +3532,16 @@
     </row>
     <row r="97" spans="1:5" ht="60" customHeight="1">
       <c r="A97" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="B97" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="B97" s="13" t="s">
+      <c r="C97" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="D97" s="11" t="s">
         <v>351</v>
-      </c>
-      <c r="C97" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="D97" s="11" t="s">
-        <v>352</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>19</v>
@@ -3468,33 +3549,33 @@
     </row>
     <row r="98" spans="1:5" ht="60" customHeight="1">
       <c r="A98" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="B98" s="12" t="s">
         <v>353</v>
-      </c>
-      <c r="B98" s="12" t="s">
-        <v>354</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E98" s="5" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="60" customHeight="1">
-      <c r="A99" s="24" t="s">
+      <c r="A99" s="27" t="s">
+        <v>355</v>
+      </c>
+      <c r="B99" s="9" t="s">
         <v>356</v>
       </c>
-      <c r="B99" s="9" t="s">
+      <c r="C99" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="D99" s="9" t="s">
         <v>357</v>
-      </c>
-      <c r="C99" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="D99" s="9" t="s">
-        <v>358</v>
       </c>
       <c r="E99" s="11" t="s">
         <v>171</v>
@@ -3502,16 +3583,16 @@
     </row>
     <row r="100" spans="1:5" ht="60" customHeight="1">
       <c r="A100" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="B100" s="12" t="s">
         <v>359</v>
       </c>
-      <c r="B100" s="12" t="s">
+      <c r="C100" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="C100" s="5" t="s">
+      <c r="D100" s="5" t="s">
         <v>361</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>362</v>
       </c>
       <c r="E100" s="5" t="s">
         <v>214</v>
@@ -3519,16 +3600,14 @@
     </row>
     <row r="101" spans="1:5" ht="60" customHeight="1">
       <c r="A101" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="B101" s="9" t="s">
-        <v>364</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="B101" s="32" t="s"/>
       <c r="C101" s="10" t="s">
         <v>52</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E101" s="11" t="s">
         <v>214</v>
@@ -3536,53 +3615,53 @@
     </row>
     <row r="102" spans="1:5" ht="60" customHeight="1">
       <c r="A102" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="B102" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="C102" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="B102" s="12" t="s">
+      <c r="D102" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="C102" s="5" t="s">
+      <c r="E102" s="5" t="s">
         <v>368</v>
-      </c>
-      <c r="D102" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="E102" s="5" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="60" customHeight="1">
       <c r="A103" s="11" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C103" s="10" t="s">
         <v>52</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E103" s="11" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="60" customHeight="1">
       <c r="A104" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="B104" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="D104" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="B104" s="12" t="s">
+      <c r="E104" s="5" t="s">
         <v>375</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="D104" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="E104" s="5" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="60" customHeight="1">
@@ -3590,20 +3669,20 @@
         <v>70</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C105" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="D105" s="30" t="s"/>
-      <c r="E105" s="30" t="s"/>
+      <c r="D105" s="31" t="s"/>
+      <c r="E105" s="31" t="s"/>
     </row>
     <row r="106" spans="1:5" ht="60" customHeight="1">
       <c r="A106" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C106" s="5" t="s"/>
       <c r="D106" s="5" t="s"/>
@@ -3611,33 +3690,33 @@
     </row>
     <row r="107" spans="1:5" ht="60" customHeight="1">
       <c r="A107" s="16" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B107" s="13" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C107" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D107" s="30" t="s">
-        <v>383</v>
-      </c>
-      <c r="E107" s="30" t="s">
-        <v>384</v>
+      <c r="D107" s="31" t="s">
+        <v>381</v>
+      </c>
+      <c r="E107" s="31" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="60" customHeight="1">
       <c r="A108" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="B108" s="14" t="s">
+        <v>384</v>
+      </c>
+      <c r="C108" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="B108" s="14" t="s">
+      <c r="D108" s="5" t="s">
         <v>386</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="D108" s="5" t="s">
-        <v>388</v>
       </c>
       <c r="E108" s="5" t="s">
         <v>167</v>
@@ -3645,31 +3724,31 @@
     </row>
     <row r="109" spans="1:5" ht="60" customHeight="1">
       <c r="A109" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="B109" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="C109" s="10" t="s">
         <v>389</v>
       </c>
-      <c r="B109" s="9" t="s">
+      <c r="D109" s="31" t="s"/>
+      <c r="E109" s="31" t="s">
         <v>390</v>
-      </c>
-      <c r="C109" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="D109" s="30" t="s"/>
-      <c r="E109" s="30" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="60" customHeight="1">
       <c r="A110" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="B110" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="C110" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="B110" s="14" t="s">
+      <c r="D110" s="5" t="s">
         <v>394</v>
-      </c>
-      <c r="C110" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="D110" s="5" t="s">
-        <v>396</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>46</v>
@@ -3677,33 +3756,33 @@
     </row>
     <row r="111" spans="1:5" ht="60" customHeight="1">
       <c r="A111" s="11" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C111" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D111" s="30" t="s">
-        <v>399</v>
-      </c>
-      <c r="E111" s="30" t="s">
+      <c r="D111" s="31" t="s">
+        <v>397</v>
+      </c>
+      <c r="E111" s="31" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="60" customHeight="1">
       <c r="A112" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B112" s="14" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C112" s="5" t="s">
         <v>52</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E112" s="5" t="s">
         <v>46</v>
@@ -3711,334 +3790,408 @@
     </row>
     <row r="113" spans="1:5" ht="60" customHeight="1">
       <c r="A113" s="11" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B113" s="13" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C113" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D113" s="30" t="s">
-        <v>405</v>
-      </c>
-      <c r="E113" s="30" t="s">
-        <v>384</v>
+      <c r="D113" s="31" t="s">
+        <v>403</v>
+      </c>
+      <c r="E113" s="31" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="60" customHeight="1">
       <c r="A114" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="B114" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="C114" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="B114" s="12" t="s">
+      <c r="D114" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="C114" s="5" t="s">
+      <c r="E114" s="5" t="s">
         <v>408</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="E114" s="5" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="60" customHeight="1">
       <c r="A115" s="11" t="s">
+        <v>409</v>
+      </c>
+      <c r="B115" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="C115" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="D115" s="11" t="s">
         <v>411</v>
       </c>
-      <c r="B115" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="C115" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="D115" s="30" t="s">
-        <v>413</v>
-      </c>
-      <c r="E115" s="30" t="s">
-        <v>410</v>
+      <c r="E115" s="31" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="60" customHeight="1">
       <c r="A116" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="B116" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="C116" s="5" t="s">
         <v>414</v>
       </c>
-      <c r="B116" s="12" t="s">
+      <c r="D116" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="C116" s="5" t="s"/>
-      <c r="D116" s="5" t="s"/>
-      <c r="E116" s="5" t="s"/>
+      <c r="E116" s="5" t="s">
+        <v>416</v>
+      </c>
     </row>
     <row r="117" spans="1:5" ht="60" customHeight="1">
       <c r="A117" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="D117" s="30" t="s">
-        <v>418</v>
-      </c>
-      <c r="E117" s="30" t="s">
-        <v>223</v>
+        <v>266</v>
+      </c>
+      <c r="D117" s="31" t="s">
+        <v>419</v>
+      </c>
+      <c r="E117" s="31" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="60" customHeight="1">
-      <c r="A118" s="4" t="s"/>
-      <c r="B118" s="12" t="s"/>
-      <c r="C118" s="5" t="s"/>
-      <c r="D118" s="5" t="s"/>
-      <c r="E118" s="5" t="s"/>
+      <c r="A118" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="B118" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D118" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="E118" s="5" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="119" spans="1:5" ht="60" customHeight="1">
-      <c r="A119" s="11" t="s"/>
-      <c r="B119" s="9" t="s"/>
-      <c r="C119" s="10" t="s"/>
-      <c r="D119" s="30" t="s"/>
-      <c r="E119" s="30" t="s"/>
+      <c r="A119" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="B119" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="C119" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D119" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="E119" s="31" t="s">
+        <v>427</v>
+      </c>
     </row>
     <row r="120" spans="1:5" ht="60" customHeight="1">
-      <c r="A120" s="4" t="s"/>
-      <c r="B120" s="12" t="s"/>
-      <c r="C120" s="5" t="s"/>
-      <c r="D120" s="5" t="s"/>
-      <c r="E120" s="5" t="s"/>
+      <c r="A120" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="B120" s="14" t="s">
+        <v>429</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="E120" s="5" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="121" spans="1:5" ht="60" customHeight="1">
-      <c r="A121" s="11" t="s"/>
-      <c r="B121" s="9" t="s"/>
-      <c r="C121" s="10" t="s"/>
-      <c r="D121" s="30" t="s"/>
-      <c r="E121" s="30" t="s"/>
+      <c r="A121" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="B121" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="C121" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="D121" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="E121" s="31" t="s"/>
     </row>
     <row r="122" spans="1:5" ht="60" customHeight="1">
-      <c r="A122" s="4" t="s"/>
-      <c r="B122" s="12" t="s"/>
-      <c r="C122" s="5" t="s"/>
-      <c r="D122" s="5" t="s"/>
-      <c r="E122" s="5" t="s"/>
+      <c r="A122" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="B122" s="33" t="s">
+        <v>437</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="E122" s="34">
+        <v>6</v>
+      </c>
     </row>
     <row r="123" spans="1:5" ht="60" customHeight="1">
-      <c r="A123" s="11" t="s"/>
-      <c r="B123" s="9" t="s"/>
-      <c r="C123" s="10" t="s"/>
-      <c r="D123" s="30" t="s"/>
-      <c r="E123" s="30" t="s"/>
+      <c r="A123" s="11" t="s">
+        <v>439</v>
+      </c>
+      <c r="B123" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="C123" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D123" s="31" t="s">
+        <v>446</v>
+      </c>
+      <c r="E123" s="11" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="124" spans="1:5" ht="60" customHeight="1">
-      <c r="A124" s="4" t="s"/>
-      <c r="B124" s="12" t="s"/>
-      <c r="C124" s="5" t="s"/>
-      <c r="D124" s="5" t="s"/>
-      <c r="E124" s="5" t="s"/>
+      <c r="A124" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="B124" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D124" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="E124" s="5" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="125" spans="1:5" ht="60" customHeight="1">
       <c r="A125" s="11" t="s"/>
-      <c r="B125" s="9" t="s"/>
+      <c r="B125" s="35" t="s"/>
       <c r="C125" s="10" t="s"/>
-      <c r="D125" s="30" t="s"/>
-      <c r="E125" s="30" t="s"/>
+      <c r="D125" s="31" t="s"/>
+      <c r="E125" s="31" t="s"/>
     </row>
     <row r="126" spans="1:5" ht="60" customHeight="1">
       <c r="A126" s="4" t="s"/>
-      <c r="B126" s="12" t="s"/>
+      <c r="B126" s="33" t="s"/>
       <c r="C126" s="5" t="s"/>
       <c r="D126" s="5" t="s"/>
       <c r="E126" s="5" t="s"/>
     </row>
     <row r="127" spans="1:5" ht="60" customHeight="1">
       <c r="A127" s="11" t="s"/>
-      <c r="B127" s="9" t="s"/>
+      <c r="B127" s="35" t="s"/>
       <c r="C127" s="10" t="s"/>
-      <c r="D127" s="30" t="s"/>
-      <c r="E127" s="30" t="s"/>
+      <c r="D127" s="31" t="s"/>
+      <c r="E127" s="31" t="s"/>
     </row>
     <row r="128" spans="1:5" ht="60" customHeight="1">
       <c r="A128" s="4" t="s"/>
-      <c r="B128" s="12" t="s"/>
+      <c r="B128" s="33" t="s"/>
       <c r="C128" s="5" t="s"/>
       <c r="D128" s="5" t="s"/>
       <c r="E128" s="5" t="s"/>
     </row>
     <row r="129" spans="1:5" ht="60" customHeight="1">
       <c r="A129" s="11" t="s"/>
-      <c r="B129" s="9" t="s"/>
+      <c r="B129" s="35" t="s"/>
       <c r="C129" s="10" t="s"/>
-      <c r="D129" s="30" t="s"/>
-      <c r="E129" s="30" t="s"/>
+      <c r="D129" s="31" t="s"/>
+      <c r="E129" s="31" t="s"/>
     </row>
     <row r="130" spans="1:5" ht="60" customHeight="1">
       <c r="A130" s="4" t="s"/>
-      <c r="B130" s="12" t="s"/>
+      <c r="B130" s="33" t="s"/>
       <c r="C130" s="5" t="s"/>
       <c r="D130" s="5" t="s"/>
       <c r="E130" s="5" t="s"/>
     </row>
     <row r="131" spans="1:5" ht="60" customHeight="1">
       <c r="A131" s="11" t="s"/>
-      <c r="B131" s="9" t="s"/>
+      <c r="B131" s="35" t="s"/>
       <c r="C131" s="10" t="s"/>
-      <c r="D131" s="30" t="s"/>
-      <c r="E131" s="30" t="s"/>
+      <c r="D131" s="31" t="s"/>
+      <c r="E131" s="31" t="s"/>
     </row>
     <row r="132" spans="1:5" ht="60" customHeight="1">
       <c r="A132" s="4" t="s"/>
-      <c r="B132" s="12" t="s"/>
+      <c r="B132" s="33" t="s"/>
       <c r="C132" s="5" t="s"/>
       <c r="D132" s="5" t="s"/>
       <c r="E132" s="5" t="s"/>
     </row>
     <row r="133" spans="1:5" ht="60" customHeight="1">
       <c r="A133" s="11" t="s"/>
-      <c r="B133" s="9" t="s"/>
+      <c r="B133" s="35" t="s"/>
       <c r="C133" s="10" t="s"/>
-      <c r="D133" s="30" t="s"/>
-      <c r="E133" s="30" t="s"/>
+      <c r="D133" s="31" t="s"/>
+      <c r="E133" s="31" t="s"/>
     </row>
     <row r="134" spans="1:5" ht="60" customHeight="1">
       <c r="A134" s="4" t="s"/>
-      <c r="B134" s="12" t="s"/>
+      <c r="B134" s="33" t="s"/>
       <c r="C134" s="5" t="s"/>
       <c r="D134" s="5" t="s"/>
       <c r="E134" s="5" t="s"/>
     </row>
     <row r="135" spans="1:5" ht="60" customHeight="1">
       <c r="A135" s="11" t="s"/>
-      <c r="B135" s="9" t="s"/>
+      <c r="B135" s="35" t="s"/>
       <c r="C135" s="10" t="s"/>
-      <c r="D135" s="30" t="s"/>
-      <c r="E135" s="30" t="s"/>
+      <c r="D135" s="31" t="s"/>
+      <c r="E135" s="31" t="s"/>
     </row>
     <row r="136" spans="1:5" ht="60" customHeight="1">
       <c r="A136" s="4" t="s"/>
-      <c r="B136" s="12" t="s"/>
+      <c r="B136" s="33" t="s"/>
       <c r="C136" s="5" t="s"/>
       <c r="D136" s="5" t="s"/>
       <c r="E136" s="5" t="s"/>
     </row>
     <row r="137" spans="1:5" ht="60" customHeight="1">
       <c r="A137" s="11" t="s"/>
-      <c r="B137" s="9" t="s"/>
+      <c r="B137" s="35" t="s"/>
       <c r="C137" s="10" t="s"/>
-      <c r="D137" s="30" t="s"/>
-      <c r="E137" s="30" t="s"/>
+      <c r="D137" s="31" t="s"/>
+      <c r="E137" s="31" t="s"/>
     </row>
     <row r="138" spans="1:5" ht="60" customHeight="1">
       <c r="A138" s="4" t="s"/>
-      <c r="B138" s="12" t="s"/>
+      <c r="B138" s="33" t="s"/>
       <c r="C138" s="5" t="s"/>
       <c r="D138" s="5" t="s"/>
       <c r="E138" s="5" t="s"/>
     </row>
     <row r="139" spans="1:5" ht="60" customHeight="1">
       <c r="A139" s="11" t="s"/>
-      <c r="B139" s="9" t="s"/>
+      <c r="B139" s="35" t="s"/>
       <c r="C139" s="10" t="s"/>
-      <c r="D139" s="30" t="s"/>
-      <c r="E139" s="30" t="s"/>
+      <c r="D139" s="31" t="s"/>
+      <c r="E139" s="31" t="s"/>
     </row>
     <row r="140" spans="1:5" ht="60" customHeight="1">
       <c r="A140" s="4" t="s"/>
-      <c r="B140" s="12" t="s"/>
+      <c r="B140" s="33" t="s"/>
       <c r="C140" s="5" t="s"/>
       <c r="D140" s="5" t="s"/>
       <c r="E140" s="5" t="s"/>
     </row>
     <row r="141" spans="1:5" ht="60" customHeight="1">
       <c r="A141" s="11" t="s"/>
-      <c r="B141" s="9" t="s"/>
+      <c r="B141" s="35" t="s"/>
       <c r="C141" s="10" t="s"/>
-      <c r="D141" s="30" t="s"/>
-      <c r="E141" s="30" t="s"/>
+      <c r="D141" s="31" t="s"/>
+      <c r="E141" s="31" t="s"/>
     </row>
     <row r="142" spans="1:5" ht="60" customHeight="1">
       <c r="A142" s="4" t="s"/>
-      <c r="B142" s="12" t="s"/>
+      <c r="B142" s="33" t="s"/>
       <c r="C142" s="5" t="s"/>
       <c r="D142" s="5" t="s"/>
       <c r="E142" s="5" t="s"/>
     </row>
     <row r="143" spans="1:5" ht="60" customHeight="1">
       <c r="A143" s="11" t="s"/>
-      <c r="B143" s="9" t="s"/>
+      <c r="B143" s="35" t="s"/>
       <c r="C143" s="10" t="s"/>
-      <c r="D143" s="30" t="s"/>
-      <c r="E143" s="30" t="s"/>
+      <c r="D143" s="31" t="s"/>
+      <c r="E143" s="31" t="s"/>
     </row>
     <row r="144" spans="1:5" ht="60" customHeight="1">
       <c r="A144" s="4" t="s"/>
-      <c r="B144" s="12" t="s"/>
+      <c r="B144" s="33" t="s"/>
       <c r="C144" s="5" t="s"/>
       <c r="D144" s="5" t="s"/>
       <c r="E144" s="5" t="s"/>
     </row>
     <row r="145" spans="1:5" ht="60" customHeight="1">
       <c r="A145" s="11" t="s"/>
-      <c r="B145" s="9" t="s"/>
+      <c r="B145" s="35" t="s"/>
       <c r="C145" s="10" t="s"/>
-      <c r="D145" s="30" t="s"/>
-      <c r="E145" s="30" t="s"/>
+      <c r="D145" s="31" t="s"/>
+      <c r="E145" s="31" t="s"/>
     </row>
     <row r="146" spans="1:5" ht="60" customHeight="1">
       <c r="A146" s="4" t="s"/>
-      <c r="B146" s="12" t="s"/>
+      <c r="B146" s="33" t="s"/>
       <c r="C146" s="5" t="s"/>
       <c r="D146" s="5" t="s"/>
       <c r="E146" s="5" t="s"/>
     </row>
     <row r="147" spans="1:5" ht="60" customHeight="1">
       <c r="A147" s="11" t="s"/>
-      <c r="B147" s="9" t="s"/>
+      <c r="B147" s="35" t="s"/>
       <c r="C147" s="10" t="s"/>
-      <c r="D147" s="30" t="s"/>
-      <c r="E147" s="30" t="s"/>
+      <c r="D147" s="31" t="s"/>
+      <c r="E147" s="31" t="s"/>
     </row>
     <row r="148" spans="1:5" ht="60" customHeight="1">
       <c r="A148" s="4" t="s"/>
-      <c r="B148" s="12" t="s"/>
+      <c r="B148" s="33" t="s"/>
       <c r="C148" s="5" t="s"/>
       <c r="D148" s="5" t="s"/>
       <c r="E148" s="5" t="s"/>
     </row>
     <row r="149" spans="1:5" ht="60" customHeight="1">
       <c r="A149" s="11" t="s"/>
-      <c r="B149" s="9" t="s"/>
+      <c r="B149" s="35" t="s"/>
       <c r="C149" s="10" t="s"/>
-      <c r="D149" s="30" t="s"/>
-      <c r="E149" s="30" t="s"/>
+      <c r="D149" s="31" t="s"/>
+      <c r="E149" s="31" t="s"/>
     </row>
     <row r="150" spans="1:5" ht="60" customHeight="1">
       <c r="A150" s="4" t="s"/>
-      <c r="B150" s="12" t="s"/>
+      <c r="B150" s="33" t="s"/>
       <c r="C150" s="5" t="s"/>
       <c r="D150" s="5" t="s"/>
       <c r="E150" s="5" t="s"/>
     </row>
     <row r="151" spans="1:5" ht="60" customHeight="1">
       <c r="A151" s="11" t="s"/>
-      <c r="B151" s="9" t="s"/>
+      <c r="B151" s="35" t="s"/>
       <c r="C151" s="10" t="s"/>
-      <c r="D151" s="30" t="s"/>
-      <c r="E151" s="30" t="s"/>
+      <c r="D151" s="31" t="s"/>
+      <c r="E151" s="31" t="s"/>
     </row>
     <row r="152" spans="1:5" ht="60" customHeight="1">
       <c r="A152" s="4" t="s"/>
-      <c r="B152" s="12" t="s"/>
+      <c r="B152" s="33" t="s"/>
       <c r="C152" s="5" t="s"/>
       <c r="D152" s="5" t="s"/>
       <c r="E152" s="5" t="s"/>
     </row>
     <row r="153" spans="1:5" ht="60" customHeight="1">
       <c r="A153" s="11" t="s"/>
-      <c r="B153" s="9" t="s"/>
+      <c r="B153" s="35" t="s"/>
       <c r="C153" s="10" t="s"/>
-      <c r="D153" s="30" t="s"/>
-      <c r="E153" s="30" t="s"/>
+      <c r="D153" s="31" t="s"/>
+      <c r="E153" s="31" t="s"/>
     </row>
     <row r="154" spans="1:5" ht="60" customHeight="1">
       <c r="A154" s="4" t="s"/>
@@ -4051,8 +4204,8 @@
       <c r="A155" s="11" t="s"/>
       <c r="B155" s="9" t="s"/>
       <c r="C155" s="10" t="s"/>
-      <c r="D155" s="30" t="s"/>
-      <c r="E155" s="30" t="s"/>
+      <c r="D155" s="31" t="s"/>
+      <c r="E155" s="31" t="s"/>
     </row>
     <row r="156" spans="1:5" ht="60" customHeight="1">
       <c r="A156" s="4" t="s"/>
@@ -4065,8 +4218,8 @@
       <c r="A157" s="11" t="s"/>
       <c r="B157" s="9" t="s"/>
       <c r="C157" s="10" t="s"/>
-      <c r="D157" s="30" t="s"/>
-      <c r="E157" s="30" t="s"/>
+      <c r="D157" s="31" t="s"/>
+      <c r="E157" s="31" t="s"/>
     </row>
     <row r="158" spans="1:5" ht="60" customHeight="1">
       <c r="A158" s="4" t="s"/>
@@ -4079,8 +4232,8 @@
       <c r="A159" s="11" t="s"/>
       <c r="B159" s="9" t="s"/>
       <c r="C159" s="10" t="s"/>
-      <c r="D159" s="30" t="s"/>
-      <c r="E159" s="30" t="s"/>
+      <c r="D159" s="31" t="s"/>
+      <c r="E159" s="31" t="s"/>
     </row>
     <row r="160" spans="1:5" ht="60" customHeight="1">
       <c r="A160" s="4" t="s"/>
@@ -4093,8 +4246,8 @@
       <c r="A161" s="11" t="s"/>
       <c r="B161" s="9" t="s"/>
       <c r="C161" s="10" t="s"/>
-      <c r="D161" s="30" t="s"/>
-      <c r="E161" s="30" t="s"/>
+      <c r="D161" s="31" t="s"/>
+      <c r="E161" s="31" t="s"/>
     </row>
     <row r="162" spans="1:5" ht="60" customHeight="1">
       <c r="A162" s="4" t="s"/>
@@ -4107,8 +4260,8 @@
       <c r="A163" s="11" t="s"/>
       <c r="B163" s="9" t="s"/>
       <c r="C163" s="10" t="s"/>
-      <c r="D163" s="30" t="s"/>
-      <c r="E163" s="30" t="s"/>
+      <c r="D163" s="31" t="s"/>
+      <c r="E163" s="31" t="s"/>
     </row>
     <row r="164" spans="1:5" ht="60" customHeight="1">
       <c r="A164" s="4" t="s"/>
@@ -4121,8 +4274,8 @@
       <c r="A165" s="11" t="s"/>
       <c r="B165" s="9" t="s"/>
       <c r="C165" s="10" t="s"/>
-      <c r="D165" s="30" t="s"/>
-      <c r="E165" s="30" t="s"/>
+      <c r="D165" s="31" t="s"/>
+      <c r="E165" s="31" t="s"/>
     </row>
     <row r="166" spans="1:5" ht="60" customHeight="1">
       <c r="A166" s="4" t="s"/>
@@ -4135,8 +4288,8 @@
       <c r="A167" s="11" t="s"/>
       <c r="B167" s="9" t="s"/>
       <c r="C167" s="10" t="s"/>
-      <c r="D167" s="30" t="s"/>
-      <c r="E167" s="30" t="s"/>
+      <c r="D167" s="31" t="s"/>
+      <c r="E167" s="31" t="s"/>
     </row>
     <row r="168" spans="1:5" ht="60" customHeight="1">
       <c r="A168" s="4" t="s"/>
@@ -4149,8 +4302,8 @@
       <c r="A169" s="11" t="s"/>
       <c r="B169" s="9" t="s"/>
       <c r="C169" s="10" t="s"/>
-      <c r="D169" s="30" t="s"/>
-      <c r="E169" s="30" t="s"/>
+      <c r="D169" s="31" t="s"/>
+      <c r="E169" s="31" t="s"/>
     </row>
     <row r="170" spans="1:5" ht="60" customHeight="1">
       <c r="A170" s="4" t="s"/>
@@ -4163,8 +4316,8 @@
       <c r="A171" s="11" t="s"/>
       <c r="B171" s="9" t="s"/>
       <c r="C171" s="10" t="s"/>
-      <c r="D171" s="30" t="s"/>
-      <c r="E171" s="30" t="s"/>
+      <c r="D171" s="31" t="s"/>
+      <c r="E171" s="31" t="s"/>
     </row>
     <row r="172" spans="1:5" ht="60" customHeight="1">
       <c r="A172" s="4" t="s"/>
@@ -4177,8 +4330,8 @@
       <c r="A173" s="11" t="s"/>
       <c r="B173" s="9" t="s"/>
       <c r="C173" s="10" t="s"/>
-      <c r="D173" s="30" t="s"/>
-      <c r="E173" s="30" t="s"/>
+      <c r="D173" s="31" t="s"/>
+      <c r="E173" s="31" t="s"/>
     </row>
     <row r="174" spans="1:5" ht="60" customHeight="1">
       <c r="A174" s="4" t="s"/>
@@ -4191,8 +4344,8 @@
       <c r="A175" s="11" t="s"/>
       <c r="B175" s="9" t="s"/>
       <c r="C175" s="10" t="s"/>
-      <c r="D175" s="30" t="s"/>
-      <c r="E175" s="30" t="s"/>
+      <c r="D175" s="31" t="s"/>
+      <c r="E175" s="31" t="s"/>
     </row>
     <row r="176" spans="1:5" ht="60" customHeight="1">
       <c r="A176" s="4" t="s"/>
@@ -4205,8 +4358,8 @@
       <c r="A177" s="11" t="s"/>
       <c r="B177" s="9" t="s"/>
       <c r="C177" s="10" t="s"/>
-      <c r="D177" s="30" t="s"/>
-      <c r="E177" s="30" t="s"/>
+      <c r="D177" s="31" t="s"/>
+      <c r="E177" s="31" t="s"/>
     </row>
     <row r="178" spans="1:5" ht="60" customHeight="1">
       <c r="A178" s="4" t="s"/>
@@ -4219,8 +4372,8 @@
       <c r="A179" s="11" t="s"/>
       <c r="B179" s="9" t="s"/>
       <c r="C179" s="10" t="s"/>
-      <c r="D179" s="30" t="s"/>
-      <c r="E179" s="30" t="s"/>
+      <c r="D179" s="31" t="s"/>
+      <c r="E179" s="31" t="s"/>
     </row>
     <row r="180" spans="1:5" ht="60" customHeight="1">
       <c r="A180" s="4" t="s"/>
@@ -4233,8 +4386,8 @@
       <c r="A181" s="11" t="s"/>
       <c r="B181" s="9" t="s"/>
       <c r="C181" s="10" t="s"/>
-      <c r="D181" s="30" t="s"/>
-      <c r="E181" s="30" t="s"/>
+      <c r="D181" s="31" t="s"/>
+      <c r="E181" s="31" t="s"/>
     </row>
     <row r="182" spans="1:5" ht="60" customHeight="1">
       <c r="A182" s="4" t="s"/>
@@ -4247,8 +4400,8 @@
       <c r="A183" s="11" t="s"/>
       <c r="B183" s="9" t="s"/>
       <c r="C183" s="10" t="s"/>
-      <c r="D183" s="30" t="s"/>
-      <c r="E183" s="30" t="s"/>
+      <c r="D183" s="31" t="s"/>
+      <c r="E183" s="31" t="s"/>
     </row>
     <row r="184" spans="1:5" ht="60" customHeight="1">
       <c r="A184" s="4" t="s"/>
@@ -4261,8 +4414,8 @@
       <c r="A185" s="11" t="s"/>
       <c r="B185" s="9" t="s"/>
       <c r="C185" s="10" t="s"/>
-      <c r="D185" s="30" t="s"/>
-      <c r="E185" s="30" t="s"/>
+      <c r="D185" s="31" t="s"/>
+      <c r="E185" s="31" t="s"/>
     </row>
     <row r="186" spans="1:5" ht="60" customHeight="1">
       <c r="A186" s="4" t="s"/>
@@ -4275,8 +4428,8 @@
       <c r="A187" s="11" t="s"/>
       <c r="B187" s="9" t="s"/>
       <c r="C187" s="10" t="s"/>
-      <c r="D187" s="30" t="s"/>
-      <c r="E187" s="30" t="s"/>
+      <c r="D187" s="31" t="s"/>
+      <c r="E187" s="31" t="s"/>
     </row>
     <row r="188" spans="1:5" ht="60" customHeight="1">
       <c r="A188" s="4" t="s"/>
@@ -4289,8 +4442,8 @@
       <c r="A189" s="11" t="s"/>
       <c r="B189" s="9" t="s"/>
       <c r="C189" s="10" t="s"/>
-      <c r="D189" s="30" t="s"/>
-      <c r="E189" s="30" t="s"/>
+      <c r="D189" s="31" t="s"/>
+      <c r="E189" s="31" t="s"/>
     </row>
     <row r="190" spans="1:5" ht="60" customHeight="1">
       <c r="A190" s="4" t="s"/>
@@ -4303,8 +4456,8 @@
       <c r="A191" s="11" t="s"/>
       <c r="B191" s="9" t="s"/>
       <c r="C191" s="10" t="s"/>
-      <c r="D191" s="30" t="s"/>
-      <c r="E191" s="30" t="s"/>
+      <c r="D191" s="31" t="s"/>
+      <c r="E191" s="31" t="s"/>
     </row>
     <row r="192" spans="1:5" ht="60" customHeight="1">
       <c r="A192" s="4" t="s"/>
@@ -4317,8 +4470,8 @@
       <c r="A193" s="11" t="s"/>
       <c r="B193" s="9" t="s"/>
       <c r="C193" s="10" t="s"/>
-      <c r="D193" s="30" t="s"/>
-      <c r="E193" s="30" t="s"/>
+      <c r="D193" s="31" t="s"/>
+      <c r="E193" s="31" t="s"/>
     </row>
     <row r="194" spans="1:5" ht="60" customHeight="1">
       <c r="A194" s="4" t="s"/>
@@ -4331,8 +4484,8 @@
       <c r="A195" s="11" t="s"/>
       <c r="B195" s="9" t="s"/>
       <c r="C195" s="10" t="s"/>
-      <c r="D195" s="30" t="s"/>
-      <c r="E195" s="30" t="s"/>
+      <c r="D195" s="31" t="s"/>
+      <c r="E195" s="31" t="s"/>
     </row>
     <row r="196" spans="1:5" ht="60" customHeight="1">
       <c r="A196" s="4" t="s"/>
@@ -4345,8 +4498,8 @@
       <c r="A197" s="11" t="s"/>
       <c r="B197" s="9" t="s"/>
       <c r="C197" s="10" t="s"/>
-      <c r="D197" s="30" t="s"/>
-      <c r="E197" s="30" t="s"/>
+      <c r="D197" s="31" t="s"/>
+      <c r="E197" s="31" t="s"/>
     </row>
     <row r="198" spans="1:5" ht="60" customHeight="1">
       <c r="A198" s="4" t="s"/>
@@ -4359,8 +4512,8 @@
       <c r="A199" s="11" t="s"/>
       <c r="B199" s="9" t="s"/>
       <c r="C199" s="10" t="s"/>
-      <c r="D199" s="30" t="s"/>
-      <c r="E199" s="30" t="s"/>
+      <c r="D199" s="31" t="s"/>
+      <c r="E199" s="31" t="s"/>
     </row>
     <row r="200" spans="1:5" ht="60" customHeight="1">
       <c r="A200" s="4" t="s"/>
@@ -4373,8 +4526,8 @@
       <c r="A201" s="11" t="s"/>
       <c r="B201" s="9" t="s"/>
       <c r="C201" s="10" t="s"/>
-      <c r="D201" s="30" t="s"/>
-      <c r="E201" s="30" t="s"/>
+      <c r="D201" s="31" t="s"/>
+      <c r="E201" s="31" t="s"/>
     </row>
     <row r="202" spans="1:5" ht="60" customHeight="1">
       <c r="A202" s="4" t="s"/>
@@ -4387,8 +4540,8 @@
       <c r="A203" s="11" t="s"/>
       <c r="B203" s="9" t="s"/>
       <c r="C203" s="10" t="s"/>
-      <c r="D203" s="30" t="s"/>
-      <c r="E203" s="30" t="s"/>
+      <c r="D203" s="31" t="s"/>
+      <c r="E203" s="31" t="s"/>
     </row>
     <row r="204" spans="1:5" ht="60" customHeight="1">
       <c r="A204" s="4" t="s"/>
@@ -4401,8 +4554,8 @@
       <c r="A205" s="11" t="s"/>
       <c r="B205" s="9" t="s"/>
       <c r="C205" s="10" t="s"/>
-      <c r="D205" s="30" t="s"/>
-      <c r="E205" s="30" t="s"/>
+      <c r="D205" s="31" t="s"/>
+      <c r="E205" s="31" t="s"/>
     </row>
     <row r="206" spans="1:5" ht="60" customHeight="1">
       <c r="A206" s="4" t="s"/>
@@ -4415,8 +4568,8 @@
       <c r="A207" s="11" t="s"/>
       <c r="B207" s="9" t="s"/>
       <c r="C207" s="10" t="s"/>
-      <c r="D207" s="30" t="s"/>
-      <c r="E207" s="30" t="s"/>
+      <c r="D207" s="31" t="s"/>
+      <c r="E207" s="31" t="s"/>
     </row>
     <row r="208" spans="1:5" ht="60" customHeight="1">
       <c r="A208" s="4" t="s"/>
@@ -4429,8 +4582,8 @@
       <c r="A209" s="11" t="s"/>
       <c r="B209" s="9" t="s"/>
       <c r="C209" s="10" t="s"/>
-      <c r="D209" s="30" t="s"/>
-      <c r="E209" s="30" t="s"/>
+      <c r="D209" s="31" t="s"/>
+      <c r="E209" s="31" t="s"/>
     </row>
     <row r="210" spans="1:5" ht="60" customHeight="1">
       <c r="A210" s="4" t="s"/>
@@ -4443,8 +4596,8 @@
       <c r="A211" s="11" t="s"/>
       <c r="B211" s="9" t="s"/>
       <c r="C211" s="10" t="s"/>
-      <c r="D211" s="30" t="s"/>
-      <c r="E211" s="30" t="s"/>
+      <c r="D211" s="31" t="s"/>
+      <c r="E211" s="31" t="s"/>
     </row>
     <row r="212" spans="1:5" ht="60" customHeight="1">
       <c r="A212" s="4" t="s"/>
@@ -4457,8 +4610,8 @@
       <c r="A213" s="11" t="s"/>
       <c r="B213" s="9" t="s"/>
       <c r="C213" s="10" t="s"/>
-      <c r="D213" s="30" t="s"/>
-      <c r="E213" s="30" t="s"/>
+      <c r="D213" s="31" t="s"/>
+      <c r="E213" s="31" t="s"/>
     </row>
     <row r="214" spans="1:5" ht="60" customHeight="1">
       <c r="A214" s="4" t="s"/>
@@ -4471,8 +4624,8 @@
       <c r="A215" s="11" t="s"/>
       <c r="B215" s="9" t="s"/>
       <c r="C215" s="10" t="s"/>
-      <c r="D215" s="30" t="s"/>
-      <c r="E215" s="30" t="s"/>
+      <c r="D215" s="31" t="s"/>
+      <c r="E215" s="31" t="s"/>
     </row>
     <row r="216" spans="1:5" ht="60" customHeight="1">
       <c r="A216" s="4" t="s"/>
@@ -4485,8 +4638,8 @@
       <c r="A217" s="11" t="s"/>
       <c r="B217" s="9" t="s"/>
       <c r="C217" s="10" t="s"/>
-      <c r="D217" s="30" t="s"/>
-      <c r="E217" s="30" t="s"/>
+      <c r="D217" s="31" t="s"/>
+      <c r="E217" s="31" t="s"/>
     </row>
     <row r="218" spans="1:5" ht="60" customHeight="1">
       <c r="A218" s="4" t="s"/>
@@ -4499,8 +4652,8 @@
       <c r="A219" s="11" t="s"/>
       <c r="B219" s="9" t="s"/>
       <c r="C219" s="10" t="s"/>
-      <c r="D219" s="30" t="s"/>
-      <c r="E219" s="30" t="s"/>
+      <c r="D219" s="31" t="s"/>
+      <c r="E219" s="31" t="s"/>
     </row>
     <row r="220" spans="1:5" ht="60" customHeight="1">
       <c r="A220" s="4" t="s"/>
@@ -4513,8 +4666,8 @@
       <c r="A221" s="11" t="s"/>
       <c r="B221" s="9" t="s"/>
       <c r="C221" s="10" t="s"/>
-      <c r="D221" s="30" t="s"/>
-      <c r="E221" s="30" t="s"/>
+      <c r="D221" s="31" t="s"/>
+      <c r="E221" s="31" t="s"/>
     </row>
     <row r="222" spans="1:5" ht="60" customHeight="1">
       <c r="A222" s="4" t="s"/>
@@ -4527,8 +4680,8 @@
       <c r="A223" s="11" t="s"/>
       <c r="B223" s="9" t="s"/>
       <c r="C223" s="10" t="s"/>
-      <c r="D223" s="30" t="s"/>
-      <c r="E223" s="30" t="s"/>
+      <c r="D223" s="31" t="s"/>
+      <c r="E223" s="31" t="s"/>
     </row>
     <row r="224" spans="1:5" ht="60" customHeight="1">
       <c r="A224" s="4" t="s"/>
@@ -4541,8 +4694,8 @@
       <c r="A225" s="11" t="s"/>
       <c r="B225" s="9" t="s"/>
       <c r="C225" s="10" t="s"/>
-      <c r="D225" s="30" t="s"/>
-      <c r="E225" s="30" t="s"/>
+      <c r="D225" s="31" t="s"/>
+      <c r="E225" s="31" t="s"/>
     </row>
     <row r="226" spans="1:5" ht="60" customHeight="1">
       <c r="A226" s="4" t="s"/>
@@ -4555,8 +4708,8 @@
       <c r="A227" s="11" t="s"/>
       <c r="B227" s="9" t="s"/>
       <c r="C227" s="10" t="s"/>
-      <c r="D227" s="30" t="s"/>
-      <c r="E227" s="30" t="s"/>
+      <c r="D227" s="31" t="s"/>
+      <c r="E227" s="31" t="s"/>
     </row>
     <row r="228" spans="1:5" ht="60" customHeight="1">
       <c r="A228" s="4" t="s"/>
@@ -4569,8 +4722,8 @@
       <c r="A229" s="11" t="s"/>
       <c r="B229" s="9" t="s"/>
       <c r="C229" s="10" t="s"/>
-      <c r="D229" s="30" t="s"/>
-      <c r="E229" s="30" t="s"/>
+      <c r="D229" s="31" t="s"/>
+      <c r="E229" s="31" t="s"/>
     </row>
     <row r="230" spans="1:5" ht="60" customHeight="1">
       <c r="A230" s="4" t="s"/>
@@ -4583,8 +4736,8 @@
       <c r="A231" s="11" t="s"/>
       <c r="B231" s="9" t="s"/>
       <c r="C231" s="10" t="s"/>
-      <c r="D231" s="30" t="s"/>
-      <c r="E231" s="30" t="s"/>
+      <c r="D231" s="31" t="s"/>
+      <c r="E231" s="31" t="s"/>
     </row>
     <row r="232" spans="1:5" ht="60" customHeight="1">
       <c r="A232" s="4" t="s"/>
@@ -4597,8 +4750,8 @@
       <c r="A233" s="11" t="s"/>
       <c r="B233" s="9" t="s"/>
       <c r="C233" s="10" t="s"/>
-      <c r="D233" s="30" t="s"/>
-      <c r="E233" s="30" t="s"/>
+      <c r="D233" s="31" t="s"/>
+      <c r="E233" s="31" t="s"/>
     </row>
     <row r="234" spans="1:5" ht="60" customHeight="1">
       <c r="A234" s="4" t="s"/>
@@ -4611,8 +4764,8 @@
       <c r="A235" s="11" t="s"/>
       <c r="B235" s="9" t="s"/>
       <c r="C235" s="10" t="s"/>
-      <c r="D235" s="30" t="s"/>
-      <c r="E235" s="30" t="s"/>
+      <c r="D235" s="31" t="s"/>
+      <c r="E235" s="31" t="s"/>
     </row>
     <row r="236" spans="1:5" ht="60" customHeight="1">
       <c r="A236" s="4" t="s"/>
@@ -4625,8 +4778,8 @@
       <c r="A237" s="11" t="s"/>
       <c r="B237" s="9" t="s"/>
       <c r="C237" s="10" t="s"/>
-      <c r="D237" s="30" t="s"/>
-      <c r="E237" s="30" t="s"/>
+      <c r="D237" s="31" t="s"/>
+      <c r="E237" s="31" t="s"/>
     </row>
     <row r="238" spans="1:5" ht="60" customHeight="1">
       <c r="A238" s="4" t="s"/>
@@ -4639,8 +4792,8 @@
       <c r="A239" s="11" t="s"/>
       <c r="B239" s="9" t="s"/>
       <c r="C239" s="10" t="s"/>
-      <c r="D239" s="30" t="s"/>
-      <c r="E239" s="30" t="s"/>
+      <c r="D239" s="31" t="s"/>
+      <c r="E239" s="31" t="s"/>
     </row>
     <row r="240" spans="1:5" ht="60" customHeight="1">
       <c r="A240" s="4" t="s"/>
@@ -4653,8 +4806,8 @@
       <c r="A241" s="11" t="s"/>
       <c r="B241" s="9" t="s"/>
       <c r="C241" s="10" t="s"/>
-      <c r="D241" s="30" t="s"/>
-      <c r="E241" s="30" t="s"/>
+      <c r="D241" s="31" t="s"/>
+      <c r="E241" s="31" t="s"/>
     </row>
     <row r="242" spans="1:5" ht="60" customHeight="1">
       <c r="A242" s="4" t="s"/>
@@ -4667,8 +4820,8 @@
       <c r="A243" s="11" t="s"/>
       <c r="B243" s="9" t="s"/>
       <c r="C243" s="10" t="s"/>
-      <c r="D243" s="30" t="s"/>
-      <c r="E243" s="30" t="s"/>
+      <c r="D243" s="31" t="s"/>
+      <c r="E243" s="31" t="s"/>
     </row>
     <row r="244" spans="1:5" ht="60" customHeight="1">
       <c r="A244" s="4" t="s"/>
@@ -4681,8 +4834,8 @@
       <c r="A245" s="11" t="s"/>
       <c r="B245" s="9" t="s"/>
       <c r="C245" s="10" t="s"/>
-      <c r="D245" s="30" t="s"/>
-      <c r="E245" s="30" t="s"/>
+      <c r="D245" s="31" t="s"/>
+      <c r="E245" s="31" t="s"/>
     </row>
     <row r="246" spans="1:5" ht="60" customHeight="1">
       <c r="A246" s="4" t="s"/>
@@ -4695,8 +4848,8 @@
       <c r="A247" s="11" t="s"/>
       <c r="B247" s="9" t="s"/>
       <c r="C247" s="10" t="s"/>
-      <c r="D247" s="30" t="s"/>
-      <c r="E247" s="30" t="s"/>
+      <c r="D247" s="31" t="s"/>
+      <c r="E247" s="31" t="s"/>
     </row>
     <row r="248" spans="1:5" ht="60" customHeight="1">
       <c r="A248" s="4" t="s"/>
@@ -4709,8 +4862,8 @@
       <c r="A249" s="11" t="s"/>
       <c r="B249" s="9" t="s"/>
       <c r="C249" s="10" t="s"/>
-      <c r="D249" s="30" t="s"/>
-      <c r="E249" s="30" t="s"/>
+      <c r="D249" s="31" t="s"/>
+      <c r="E249" s="31" t="s"/>
     </row>
     <row r="250" spans="1:5" ht="60" customHeight="1">
       <c r="A250" s="4" t="s"/>
@@ -4723,8 +4876,8 @@
       <c r="A251" s="11" t="s"/>
       <c r="B251" s="9" t="s"/>
       <c r="C251" s="10" t="s"/>
-      <c r="D251" s="30" t="s"/>
-      <c r="E251" s="30" t="s"/>
+      <c r="D251" s="31" t="s"/>
+      <c r="E251" s="31" t="s"/>
     </row>
     <row r="252" spans="1:5" ht="60" customHeight="1">
       <c r="A252" s="4" t="s"/>
@@ -4737,8 +4890,8 @@
       <c r="A253" s="11" t="s"/>
       <c r="B253" s="9" t="s"/>
       <c r="C253" s="10" t="s"/>
-      <c r="D253" s="30" t="s"/>
-      <c r="E253" s="30" t="s"/>
+      <c r="D253" s="31" t="s"/>
+      <c r="E253" s="31" t="s"/>
     </row>
     <row r="254" spans="1:5" ht="60" customHeight="1">
       <c r="A254" s="4" t="s"/>
@@ -4751,8 +4904,8 @@
       <c r="A255" s="11" t="s"/>
       <c r="B255" s="9" t="s"/>
       <c r="C255" s="10" t="s"/>
-      <c r="D255" s="30" t="s"/>
-      <c r="E255" s="30" t="s"/>
+      <c r="D255" s="31" t="s"/>
+      <c r="E255" s="31" t="s"/>
     </row>
     <row r="256" spans="1:5" ht="60" customHeight="1">
       <c r="A256" s="4" t="s"/>
@@ -4765,8 +4918,8 @@
       <c r="A257" s="11" t="s"/>
       <c r="B257" s="9" t="s"/>
       <c r="C257" s="10" t="s"/>
-      <c r="D257" s="30" t="s"/>
-      <c r="E257" s="30" t="s"/>
+      <c r="D257" s="31" t="s"/>
+      <c r="E257" s="31" t="s"/>
     </row>
     <row r="258" spans="1:5" ht="60" customHeight="1">
       <c r="A258" s="4" t="s"/>
@@ -4779,8 +4932,8 @@
       <c r="A259" s="11" t="s"/>
       <c r="B259" s="9" t="s"/>
       <c r="C259" s="10" t="s"/>
-      <c r="D259" s="30" t="s"/>
-      <c r="E259" s="30" t="s"/>
+      <c r="D259" s="31" t="s"/>
+      <c r="E259" s="31" t="s"/>
     </row>
     <row r="260" spans="1:5" ht="60" customHeight="1">
       <c r="A260" s="4" t="s"/>
@@ -4793,8 +4946,8 @@
       <c r="A261" s="11" t="s"/>
       <c r="B261" s="9" t="s"/>
       <c r="C261" s="10" t="s"/>
-      <c r="D261" s="30" t="s"/>
-      <c r="E261" s="30" t="s"/>
+      <c r="D261" s="31" t="s"/>
+      <c r="E261" s="31" t="s"/>
     </row>
     <row r="262" spans="1:5" ht="60" customHeight="1">
       <c r="A262" s="4" t="s"/>
@@ -4807,8 +4960,8 @@
       <c r="A263" s="11" t="s"/>
       <c r="B263" s="9" t="s"/>
       <c r="C263" s="10" t="s"/>
-      <c r="D263" s="30" t="s"/>
-      <c r="E263" s="30" t="s"/>
+      <c r="D263" s="31" t="s"/>
+      <c r="E263" s="31" t="s"/>
     </row>
     <row r="264" spans="1:5" ht="60" customHeight="1">
       <c r="A264" s="4" t="s"/>
@@ -4821,8 +4974,8 @@
       <c r="A265" s="11" t="s"/>
       <c r="B265" s="9" t="s"/>
       <c r="C265" s="10" t="s"/>
-      <c r="D265" s="30" t="s"/>
-      <c r="E265" s="30" t="s"/>
+      <c r="D265" s="31" t="s"/>
+      <c r="E265" s="31" t="s"/>
     </row>
     <row r="266" spans="1:5" ht="60" customHeight="1">
       <c r="A266" s="4" t="s"/>
@@ -4835,8 +4988,8 @@
       <c r="A267" s="11" t="s"/>
       <c r="B267" s="9" t="s"/>
       <c r="C267" s="10" t="s"/>
-      <c r="D267" s="30" t="s"/>
-      <c r="E267" s="30" t="s"/>
+      <c r="D267" s="31" t="s"/>
+      <c r="E267" s="31" t="s"/>
     </row>
     <row r="268" spans="1:5" ht="60" customHeight="1">
       <c r="A268" s="4" t="s"/>
@@ -4849,8 +5002,8 @@
       <c r="A269" s="11" t="s"/>
       <c r="B269" s="9" t="s"/>
       <c r="C269" s="10" t="s"/>
-      <c r="D269" s="30" t="s"/>
-      <c r="E269" s="30" t="s"/>
+      <c r="D269" s="31" t="s"/>
+      <c r="E269" s="31" t="s"/>
     </row>
     <row r="270" spans="1:5" ht="60" customHeight="1">
       <c r="A270" s="4" t="s"/>
@@ -4863,8 +5016,8 @@
       <c r="A271" s="11" t="s"/>
       <c r="B271" s="9" t="s"/>
       <c r="C271" s="10" t="s"/>
-      <c r="D271" s="30" t="s"/>
-      <c r="E271" s="30" t="s"/>
+      <c r="D271" s="31" t="s"/>
+      <c r="E271" s="31" t="s"/>
     </row>
     <row r="272" spans="1:5" ht="60" customHeight="1">
       <c r="A272" s="4" t="s"/>
@@ -4877,8 +5030,8 @@
       <c r="A273" s="11" t="s"/>
       <c r="B273" s="9" t="s"/>
       <c r="C273" s="10" t="s"/>
-      <c r="D273" s="30" t="s"/>
-      <c r="E273" s="30" t="s"/>
+      <c r="D273" s="31" t="s"/>
+      <c r="E273" s="31" t="s"/>
     </row>
     <row r="274" spans="1:5" ht="60" customHeight="1">
       <c r="A274" s="4" t="s"/>
@@ -4891,8 +5044,8 @@
       <c r="A275" s="11" t="s"/>
       <c r="B275" s="9" t="s"/>
       <c r="C275" s="10" t="s"/>
-      <c r="D275" s="30" t="s"/>
-      <c r="E275" s="30" t="s"/>
+      <c r="D275" s="31" t="s"/>
+      <c r="E275" s="31" t="s"/>
     </row>
     <row r="276" spans="1:5" ht="60" customHeight="1">
       <c r="A276" s="4" t="s"/>
@@ -4905,8 +5058,8 @@
       <c r="A277" s="11" t="s"/>
       <c r="B277" s="9" t="s"/>
       <c r="C277" s="10" t="s"/>
-      <c r="D277" s="30" t="s"/>
-      <c r="E277" s="30" t="s"/>
+      <c r="D277" s="31" t="s"/>
+      <c r="E277" s="31" t="s"/>
     </row>
     <row r="278" spans="1:5" ht="60" customHeight="1">
       <c r="A278" s="4" t="s"/>
@@ -4919,8 +5072,8 @@
       <c r="A279" s="11" t="s"/>
       <c r="B279" s="9" t="s"/>
       <c r="C279" s="10" t="s"/>
-      <c r="D279" s="30" t="s"/>
-      <c r="E279" s="30" t="s"/>
+      <c r="D279" s="31" t="s"/>
+      <c r="E279" s="31" t="s"/>
     </row>
     <row r="280" spans="1:5" ht="60" customHeight="1">
       <c r="A280" s="4" t="s"/>
@@ -4933,8 +5086,8 @@
       <c r="A281" s="11" t="s"/>
       <c r="B281" s="9" t="s"/>
       <c r="C281" s="10" t="s"/>
-      <c r="D281" s="30" t="s"/>
-      <c r="E281" s="30" t="s"/>
+      <c r="D281" s="31" t="s"/>
+      <c r="E281" s="31" t="s"/>
     </row>
     <row r="282" spans="1:5" ht="60" customHeight="1">
       <c r="A282" s="4" t="s"/>
@@ -4947,8 +5100,8 @@
       <c r="A283" s="11" t="s"/>
       <c r="B283" s="9" t="s"/>
       <c r="C283" s="10" t="s"/>
-      <c r="D283" s="30" t="s"/>
-      <c r="E283" s="30" t="s"/>
+      <c r="D283" s="31" t="s"/>
+      <c r="E283" s="31" t="s"/>
     </row>
     <row r="284" spans="1:5" ht="60" customHeight="1">
       <c r="A284" s="4" t="s"/>
@@ -4961,8 +5114,8 @@
       <c r="A285" s="11" t="s"/>
       <c r="B285" s="9" t="s"/>
       <c r="C285" s="10" t="s"/>
-      <c r="D285" s="30" t="s"/>
-      <c r="E285" s="30" t="s"/>
+      <c r="D285" s="31" t="s"/>
+      <c r="E285" s="31" t="s"/>
     </row>
     <row r="286" spans="1:5" ht="60" customHeight="1">
       <c r="A286" s="4" t="s"/>
@@ -4975,8 +5128,8 @@
       <c r="A287" s="11" t="s"/>
       <c r="B287" s="9" t="s"/>
       <c r="C287" s="10" t="s"/>
-      <c r="D287" s="30" t="s"/>
-      <c r="E287" s="30" t="s"/>
+      <c r="D287" s="31" t="s"/>
+      <c r="E287" s="31" t="s"/>
     </row>
     <row r="288" spans="1:5" ht="60" customHeight="1">
       <c r="A288" s="4" t="s"/>
@@ -4989,8 +5142,8 @@
       <c r="A289" s="11" t="s"/>
       <c r="B289" s="9" t="s"/>
       <c r="C289" s="10" t="s"/>
-      <c r="D289" s="30" t="s"/>
-      <c r="E289" s="30" t="s"/>
+      <c r="D289" s="31" t="s"/>
+      <c r="E289" s="31" t="s"/>
     </row>
     <row r="290" spans="1:5" ht="60" customHeight="1">
       <c r="A290" s="4" t="s"/>
@@ -5003,8 +5156,8 @@
       <c r="A291" s="11" t="s"/>
       <c r="B291" s="9" t="s"/>
       <c r="C291" s="10" t="s"/>
-      <c r="D291" s="30" t="s"/>
-      <c r="E291" s="30" t="s"/>
+      <c r="D291" s="31" t="s"/>
+      <c r="E291" s="31" t="s"/>
     </row>
     <row r="292" spans="1:5" ht="60" customHeight="1">
       <c r="A292" s="4" t="s"/>
@@ -5017,8 +5170,8 @@
       <c r="A293" s="11" t="s"/>
       <c r="B293" s="9" t="s"/>
       <c r="C293" s="10" t="s"/>
-      <c r="D293" s="30" t="s"/>
-      <c r="E293" s="30" t="s"/>
+      <c r="D293" s="31" t="s"/>
+      <c r="E293" s="31" t="s"/>
     </row>
     <row r="294" spans="1:5" ht="60" customHeight="1">
       <c r="A294" s="4" t="s"/>
@@ -5031,8 +5184,8 @@
       <c r="A295" s="11" t="s"/>
       <c r="B295" s="9" t="s"/>
       <c r="C295" s="10" t="s"/>
-      <c r="D295" s="30" t="s"/>
-      <c r="E295" s="30" t="s"/>
+      <c r="D295" s="31" t="s"/>
+      <c r="E295" s="31" t="s"/>
     </row>
     <row r="296" spans="1:5" ht="60" customHeight="1">
       <c r="A296" s="4" t="s"/>
@@ -5045,8 +5198,8 @@
       <c r="A297" s="11" t="s"/>
       <c r="B297" s="9" t="s"/>
       <c r="C297" s="10" t="s"/>
-      <c r="D297" s="30" t="s"/>
-      <c r="E297" s="30" t="s"/>
+      <c r="D297" s="31" t="s"/>
+      <c r="E297" s="31" t="s"/>
     </row>
     <row r="298" spans="1:5" ht="60" customHeight="1">
       <c r="A298" s="4" t="s"/>
@@ -5057,10 +5210,10 @@
     </row>
     <row r="299" spans="1:5" ht="60" customHeight="1">
       <c r="A299" s="11" t="s"/>
-      <c r="B299" s="31" t="s"/>
+      <c r="B299" s="36" t="s"/>
       <c r="C299" s="10" t="s"/>
-      <c r="D299" s="30" t="s"/>
-      <c r="E299" s="30" t="s"/>
+      <c r="D299" s="31" t="s"/>
+      <c r="E299" s="31" t="s"/>
     </row>
   </sheetData>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="480">
   <si>
     <t/>
   </si>
@@ -1360,6 +1360,102 @@
   </si>
   <si>
     <t>中速 铺场</t>
+  </si>
+  <si>
+    <t>%%36|2n5C5U5W5x636B7xE8gQimjjlfmfnGnPnQp4p9qDqtx9zn;5OfcgJjOmaqz;;oG</t>
+  </si>
+  <si>
+    <t>我喜欢你</t>
+  </si>
+  <si>
+    <t>妈妈</t>
+  </si>
+  <si>
+    <t>狂三様のネコ</t>
+  </si>
+  <si>
+    <t>经典娱乐卡组。开局不要留妥协，优先找小费。金零战可以让对面出不了手牌。毁坏视情况而定，大部分情况下是偷对面手里的流星或者日研</t>
+  </si>
+  <si>
+    <t>英美防火墙*</t>
+  </si>
+  <si>
+    <t>%%25|0m0w0z191mbDgvlrofyJ;0j0n0sbr;080olu;0dlosC</t>
+  </si>
+  <si>
+    <t>少下单位，用防火墙让对面单位无法攻击总部，或者用两难困境，让对部变成大卫带。最后用流星或者是英联邦取胜。</t>
+  </si>
+  <si>
+    <t>狂三のネコ</t>
+  </si>
+  <si>
+    <t>德澳撤退</t>
+  </si>
+  <si>
+    <t>%%1a|2L2Z3Y4zgUiaoKu0;1C3i3jDJjinwoPwJwM;4xfUoX;yb</t>
+  </si>
+  <si>
+    <t>用各种牌撤退对面的单位，然后逐步建立场面优势。撤退完对面单位后，还可以用U18</t>
+  </si>
+  <si>
+    <t>用各种牌撤退对面的单位，然后逐步建立场面优势。撤退完对面单位后，还可以用U48禁止对面部署，顺手还能爆爆对面的牌。</t>
+  </si>
+  <si>
+    <t>日英炸槽</t>
+  </si>
+  <si>
+    <t>德澳撤退*</t>
+  </si>
+  <si>
+    <t>日英炸槽一*</t>
+  </si>
+  <si>
+    <t>%%32|6CnGqDtTznzq;0a0s0t1dfcjOtFzpzw;78p1p3p6tU;</t>
+  </si>
+  <si>
+    <t>慢速之友，前期炸槽，好高骛远找组件，六费左右拍金零战。顺手再拍几个黑卫士。黑卫士和金灵战可以让对面</t>
+  </si>
+  <si>
+    <t>慢速之友，前期炸槽，好高骛远找组件，六费左右拍金零战。顺手再拍几个黑卫士。黑卫士和金灵战可以让对面计划涨到8费。再加上一些妙妙反制。反制完之后，对面手牌不会减费，防止对面用低费牌嫖掉金零战特效。</t>
+  </si>
+  <si>
+    <t>日英炸槽二*</t>
+  </si>
+  <si>
+    <t>%%32|5CE8rk;0a0s1d6wjOmanIp3p4p6tFtTx3zszw;p1tK;</t>
+  </si>
+  <si>
+    <t>找组件，炸槽，定向抽或者开发最后一博。跳到10费后给对面压到零费。然后再给对面加加费。用闪击单位直接撞死对面。手牌顺的话还可以直接开完最后一搏，用7075铝。</t>
+  </si>
+  <si>
+    <t>英日炸槽剃头*</t>
+  </si>
+  <si>
+    <t>%%23|0B0w191xgFgPjeoop9v8w7;0a0j1dhDjOwax3;w2yH;DRtU</t>
+  </si>
+  <si>
+    <t>这套舍弃了，英联邦转而用剃头作为终结手段。舍弃了4费及以下的其他牌，只保留4张4费炸槽让西非旅定向抽。</t>
+  </si>
+  <si>
+    <t>这套舍弃了英联邦转而用剃头作为终结手段。舍弃了4费及以下的其他牌，只保留4张4费炸槽让西非旅定向抽。只要对面指挥点低，对面就解不掉大飞机</t>
+  </si>
+  <si>
+    <t>英日控顶*</t>
+  </si>
+  <si>
+    <t>%%23|0F0m1x1yjesQtXv8w7;0leFhPousRtW;eHp6;0gmUyH</t>
+  </si>
+  <si>
+    <t>携带了大量返回牌组顶的卡，盟日是为了那几张开发，对面下一张牌就给他扔回去一张，遇见部署效果多的卡组没办法。只要坚持扔，用不了几个回合，对面就得断水。到时候边扔边剃头，简单增好感。</t>
+  </si>
+  <si>
+    <t>英德谜语报复社会*</t>
+  </si>
+  <si>
+    <t>%%21|0B0k0mgvhDhEjeooq0sQw2w5wbyJ;080E0noqoxyH;sCtdtU;oX</t>
+  </si>
+  <si>
+    <t>玩这套不要奔着赢，这是一套社交卡组。注意点就一个权杖号和诱敌可以一起，权杖返完了之后不算作使用，如果对面看你空过两费，可能会以为挂了两张权杖。这个时候，他可能会再拿出来计划试反制，但是不会触发诱敌，当对面放心用的时候，第2张指令就会触发诱敌。然后好感度加一</t>
   </si>
 </sst>
 </file>
@@ -3734,7 +3830,7 @@
       </c>
       <c r="D109" s="31" t="s"/>
       <c r="E109" s="31" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="60" customHeight="1">
@@ -3915,7 +4011,7 @@
         <v>429</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>447</v>
+        <v>173</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>431</v>
@@ -3991,60 +4087,140 @@
       </c>
     </row>
     <row r="125" spans="1:5" ht="60" customHeight="1">
-      <c r="A125" s="11" t="s"/>
-      <c r="B125" s="35" t="s"/>
-      <c r="C125" s="10" t="s"/>
-      <c r="D125" s="31" t="s"/>
-      <c r="E125" s="31" t="s"/>
+      <c r="A125" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B125" s="35" t="s">
+        <v>448</v>
+      </c>
+      <c r="C125" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D125" s="31" t="s">
+        <v>452</v>
+      </c>
+      <c r="E125" s="31" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="126" spans="1:5" ht="60" customHeight="1">
-      <c r="A126" s="4" t="s"/>
-      <c r="B126" s="33" t="s"/>
-      <c r="C126" s="5" t="s"/>
-      <c r="D126" s="5" t="s"/>
-      <c r="E126" s="5" t="s"/>
+      <c r="A126" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="B126" s="33" t="s">
+        <v>454</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="E126" s="5" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="127" spans="1:5" ht="60" customHeight="1">
-      <c r="A127" s="11" t="s"/>
-      <c r="B127" s="35" t="s"/>
-      <c r="C127" s="10" t="s"/>
-      <c r="D127" s="31" t="s"/>
-      <c r="E127" s="31" t="s"/>
+      <c r="A127" s="11" t="s">
+        <v>462</v>
+      </c>
+      <c r="B127" s="35" t="s">
+        <v>458</v>
+      </c>
+      <c r="C127" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D127" s="31" t="s">
+        <v>460</v>
+      </c>
+      <c r="E127" s="5" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="128" spans="1:5" ht="60" customHeight="1">
-      <c r="A128" s="4" t="s"/>
-      <c r="B128" s="33" t="s"/>
-      <c r="C128" s="5" t="s"/>
-      <c r="D128" s="5" t="s"/>
-      <c r="E128" s="5" t="s"/>
+      <c r="A128" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B128" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="E128" s="5" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="129" spans="1:5" ht="60" customHeight="1">
-      <c r="A129" s="11" t="s"/>
-      <c r="B129" s="35" t="s"/>
-      <c r="C129" s="10" t="s"/>
-      <c r="D129" s="31" t="s"/>
-      <c r="E129" s="31" t="s"/>
+      <c r="A129" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B129" s="35" t="s">
+        <v>468</v>
+      </c>
+      <c r="C129" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D129" s="31" t="s">
+        <v>469</v>
+      </c>
+      <c r="E129" s="31" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="130" spans="1:5" ht="60" customHeight="1">
-      <c r="A130" s="4" t="s"/>
-      <c r="B130" s="33" t="s"/>
-      <c r="C130" s="5" t="s"/>
-      <c r="D130" s="5" t="s"/>
-      <c r="E130" s="5" t="s"/>
+      <c r="A130" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="B130" s="33" t="s">
+        <v>471</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="E130" s="5" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="131" spans="1:5" ht="60" customHeight="1">
-      <c r="A131" s="11" t="s"/>
-      <c r="B131" s="35" t="s"/>
-      <c r="C131" s="10" t="s"/>
-      <c r="D131" s="31" t="s"/>
-      <c r="E131" s="31" t="s"/>
+      <c r="A131" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="B131" s="35" t="s">
+        <v>475</v>
+      </c>
+      <c r="C131" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D131" s="31" t="s">
+        <v>476</v>
+      </c>
+      <c r="E131" s="31" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="132" spans="1:5" ht="60" customHeight="1">
-      <c r="A132" s="4" t="s"/>
-      <c r="B132" s="33" t="s"/>
-      <c r="C132" s="5" t="s"/>
-      <c r="D132" s="5" t="s"/>
-      <c r="E132" s="5" t="s"/>
+      <c r="A132" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="B132" s="33" t="s">
+        <v>478</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="E132" s="5" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="133" spans="1:5" ht="60" customHeight="1">
       <c r="A133" s="11" t="s"/>
